--- a/diseases/d124/2000-2004.xlsx
+++ b/diseases/d124/2000-2004.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
@@ -1457,9 +1454,6 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
@@ -2001,9 +1995,6 @@
       <c r="O9" t="n">
         <v>0</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
@@ -2545,9 +2536,6 @@
       <c r="O12" t="n">
         <v>1</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>0.02226741517840542</v>
       </c>
@@ -3089,9 +3077,6 @@
       <c r="O15" t="n">
         <v>0</v>
       </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
       <c r="R15" t="n">
         <v>0</v>
       </c>
@@ -3633,9 +3618,6 @@
       <c r="O18" t="n">
         <v>3</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0.06680224553521626</v>
       </c>
@@ -4177,9 +4159,6 @@
       <c r="O21" t="n">
         <v>0</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
       <c r="R21" t="n">
         <v>0</v>
       </c>
@@ -4721,9 +4700,6 @@
       <c r="O24" t="n">
         <v>3</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>0.06680224553521626</v>
       </c>
@@ -5265,9 +5241,6 @@
       <c r="O27" t="n">
         <v>0</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" t="n">
         <v>0</v>
       </c>
@@ -5809,9 +5782,6 @@
       <c r="O30" t="n">
         <v>0</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0</v>
       </c>
@@ -6353,9 +6323,6 @@
       <c r="O33" t="n">
         <v>0</v>
       </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
       <c r="R33" t="n">
         <v>0</v>
       </c>
@@ -6897,9 +6864,6 @@
       <c r="O36" t="n">
         <v>2</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>0.04453483035681084</v>
       </c>
@@ -7441,9 +7405,6 @@
       <c r="O39" t="n">
         <v>0</v>
       </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
       <c r="R39" t="n">
         <v>0</v>
       </c>
@@ -7985,9 +7946,6 @@
       <c r="O42" t="n">
         <v>1</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>0.02226741517840542</v>
       </c>
@@ -8529,9 +8487,6 @@
       <c r="O45" t="n">
         <v>0</v>
       </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
       <c r="R45" t="n">
         <v>0</v>
       </c>
@@ -9073,9 +9028,6 @@
       <c r="O48" t="n">
         <v>1</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>0.02226741517840542</v>
       </c>
@@ -9617,9 +9569,6 @@
       <c r="O51" t="n">
         <v>0</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
       <c r="R51" t="n">
         <v>0</v>
       </c>
@@ -10161,9 +10110,6 @@
       <c r="O54" t="n">
         <v>3</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>0.06680224553521626</v>
       </c>
@@ -10705,9 +10651,6 @@
       <c r="O57" t="n">
         <v>0</v>
       </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
       <c r="R57" t="n">
         <v>0</v>
       </c>
@@ -11249,9 +11192,6 @@
       <c r="O60" t="n">
         <v>1</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0.02226741517840542</v>
       </c>
@@ -11793,9 +11733,6 @@
       <c r="O63" t="n">
         <v>0</v>
       </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
       <c r="R63" t="n">
         <v>0</v>
       </c>
@@ -12337,9 +12274,6 @@
       <c r="O66" t="n">
         <v>0</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>0</v>
       </c>
@@ -12881,9 +12815,6 @@
       <c r="O69" t="n">
         <v>0</v>
       </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
       <c r="R69" t="n">
         <v>0</v>
       </c>
@@ -13425,9 +13356,6 @@
       <c r="O72" t="n">
         <v>0</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0</v>
       </c>
@@ -13969,9 +13897,6 @@
       <c r="O75" t="n">
         <v>0</v>
       </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
       <c r="R75" t="n">
         <v>0</v>
       </c>
@@ -14513,9 +14438,6 @@
       <c r="O78" t="n">
         <v>22</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>0.04676525973807884</v>
       </c>
@@ -14661,9 +14583,6 @@
       <c r="O79" t="n">
         <v>0</v>
       </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
       <c r="R79" t="n">
         <v>0</v>
       </c>
@@ -15205,9 +15124,6 @@
       <c r="O82" t="n">
         <v>0</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0</v>
       </c>
@@ -15749,9 +15665,6 @@
       <c r="O85" t="n">
         <v>19</v>
       </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
       <c r="R85" t="n">
         <v>0.04038817886470444</v>
       </c>
@@ -15897,9 +15810,6 @@
       <c r="O86" t="n">
         <v>0</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0</v>
       </c>
@@ -16441,9 +16351,6 @@
       <c r="O89" t="n">
         <v>0</v>
       </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
       <c r="R89" t="n">
         <v>0</v>
       </c>
@@ -16985,9 +16892,6 @@
       <c r="O92" t="n">
         <v>29</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>0.06164511510928573</v>
       </c>
@@ -17133,9 +17037,6 @@
       <c r="O93" t="n">
         <v>3</v>
       </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
       <c r="R93" t="n">
         <v>0.0664649529195506</v>
       </c>
@@ -17677,9 +17578,6 @@
       <c r="O96" t="n">
         <v>0</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>0</v>
       </c>
@@ -18221,9 +18119,6 @@
       <c r="O99" t="n">
         <v>118</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="R99" t="n">
         <v>0.2508318476860592</v>
       </c>
@@ -18369,9 +18264,6 @@
       <c r="O100" t="n">
         <v>4</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>0.08861993722606747</v>
       </c>
@@ -18913,9 +18805,6 @@
       <c r="O103" t="n">
         <v>0</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="R103" t="n">
         <v>0</v>
       </c>
@@ -19457,9 +19346,6 @@
       <c r="O106" t="n">
         <v>43</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="R106" t="n">
         <v>0.09140482585169954</v>
       </c>
@@ -19605,9 +19491,6 @@
       <c r="O107" t="n">
         <v>1</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>0.02215498430651687</v>
       </c>
@@ -20149,9 +20032,6 @@
       <c r="O110" t="n">
         <v>0</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>0</v>
       </c>
@@ -20693,9 +20573,6 @@
       <c r="O113" t="n">
         <v>29</v>
       </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
       <c r="R113" t="n">
         <v>0.06164511510928573</v>
       </c>
@@ -20841,9 +20718,6 @@
       <c r="O114" t="n">
         <v>3</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>0.0664649529195506</v>
       </c>
@@ -21385,9 +21259,6 @@
       <c r="O117" t="n">
         <v>0</v>
       </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
       <c r="R117" t="n">
         <v>0</v>
       </c>
@@ -21929,9 +21800,6 @@
       <c r="O120" t="n">
         <v>33</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>0.07014788960711825</v>
       </c>
@@ -22077,9 +21945,6 @@
       <c r="O121" t="n">
         <v>1</v>
       </c>
-      <c r="Q121" t="n">
-        <v>0</v>
-      </c>
       <c r="R121" t="n">
         <v>0.02215498430651687</v>
       </c>
@@ -22621,9 +22486,6 @@
       <c r="O124" t="n">
         <v>0</v>
       </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
       <c r="R124" t="n">
         <v>0</v>
       </c>
@@ -23165,9 +23027,6 @@
       <c r="O127" t="n">
         <v>20</v>
       </c>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
       <c r="R127" t="n">
         <v>0.04251387248916258</v>
       </c>
@@ -23313,9 +23172,6 @@
       <c r="O128" t="n">
         <v>1</v>
       </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
       <c r="R128" t="n">
         <v>0.02215498430651687</v>
       </c>
@@ -23857,9 +23713,6 @@
       <c r="O131" t="n">
         <v>0</v>
       </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
       <c r="R131" t="n">
         <v>0</v>
       </c>
@@ -24401,9 +24254,6 @@
       <c r="O134" t="n">
         <v>26</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="R134" t="n">
         <v>0.05526803423591135</v>
       </c>
@@ -24549,9 +24399,6 @@
       <c r="O135" t="n">
         <v>0</v>
       </c>
-      <c r="Q135" t="n">
-        <v>0</v>
-      </c>
       <c r="R135" t="n">
         <v>0</v>
       </c>
@@ -25093,9 +24940,6 @@
       <c r="O138" t="n">
         <v>1</v>
       </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
       <c r="R138" t="n">
         <v>0.01927535832409241</v>
       </c>
@@ -25637,9 +25481,6 @@
       <c r="O141" t="n">
         <v>13</v>
       </c>
-      <c r="Q141" t="n">
-        <v>0</v>
-      </c>
       <c r="R141" t="n">
         <v>0.02763401711795567</v>
       </c>
@@ -25785,9 +25626,6 @@
       <c r="O142" t="n">
         <v>3</v>
       </c>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
       <c r="R142" t="n">
         <v>0.0664649529195506</v>
       </c>
@@ -26329,9 +26167,6 @@
       <c r="O145" t="n">
         <v>0</v>
       </c>
-      <c r="Q145" t="n">
-        <v>0</v>
-      </c>
       <c r="R145" t="n">
         <v>0</v>
       </c>
@@ -26873,9 +26708,6 @@
       <c r="O148" t="n">
         <v>23</v>
       </c>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
       <c r="R148" t="n">
         <v>0.04889095336253697</v>
       </c>
@@ -27021,9 +26853,6 @@
       <c r="O149" t="n">
         <v>0</v>
       </c>
-      <c r="Q149" t="n">
-        <v>0</v>
-      </c>
       <c r="R149" t="n">
         <v>0</v>
       </c>
@@ -27565,9 +27394,6 @@
       <c r="O152" t="n">
         <v>0</v>
       </c>
-      <c r="Q152" t="n">
-        <v>0</v>
-      </c>
       <c r="R152" t="n">
         <v>0</v>
       </c>
@@ -28109,9 +27935,6 @@
       <c r="O155" t="n">
         <v>26</v>
       </c>
-      <c r="Q155" t="n">
-        <v>0</v>
-      </c>
       <c r="R155" t="n">
         <v>0.05526803423591135</v>
       </c>
@@ -28257,9 +28080,6 @@
       <c r="O156" t="n">
         <v>1</v>
       </c>
-      <c r="Q156" t="n">
-        <v>0</v>
-      </c>
       <c r="R156" t="n">
         <v>0.02215498430651687</v>
       </c>
@@ -28801,9 +28621,6 @@
       <c r="O159" t="n">
         <v>1</v>
       </c>
-      <c r="Q159" t="n">
-        <v>0</v>
-      </c>
       <c r="R159" t="n">
         <v>0.01922875021199697</v>
       </c>
@@ -29345,9 +29162,6 @@
       <c r="O162" t="n">
         <v>35</v>
       </c>
-      <c r="Q162" t="n">
-        <v>0</v>
-      </c>
       <c r="R162" t="n">
         <v>0.07399714757909716</v>
       </c>
@@ -29493,9 +29307,6 @@
       <c r="O163" t="n">
         <v>0</v>
       </c>
-      <c r="Q163" t="n">
-        <v>0</v>
-      </c>
       <c r="R163" t="n">
         <v>0</v>
       </c>
@@ -30037,9 +29848,6 @@
       <c r="O166" t="n">
         <v>0</v>
       </c>
-      <c r="Q166" t="n">
-        <v>0</v>
-      </c>
       <c r="R166" t="n">
         <v>0</v>
       </c>
@@ -30581,9 +30389,6 @@
       <c r="O169" t="n">
         <v>25</v>
       </c>
-      <c r="Q169" t="n">
-        <v>0</v>
-      </c>
       <c r="R169" t="n">
         <v>0.05285510541364083</v>
       </c>
@@ -30729,9 +30534,6 @@
       <c r="O170" t="n">
         <v>2</v>
       </c>
-      <c r="Q170" t="n">
-        <v>0</v>
-      </c>
       <c r="R170" t="n">
         <v>0.04407214257161833</v>
       </c>
@@ -31273,9 +31075,6 @@
       <c r="O173" t="n">
         <v>0</v>
       </c>
-      <c r="Q173" t="n">
-        <v>0</v>
-      </c>
       <c r="R173" t="n">
         <v>0</v>
       </c>
@@ -31817,9 +31616,6 @@
       <c r="O176" t="n">
         <v>22</v>
       </c>
-      <c r="Q176" t="n">
-        <v>0</v>
-      </c>
       <c r="R176" t="n">
         <v>0.04651249276400393</v>
       </c>
@@ -31965,9 +31761,6 @@
       <c r="O177" t="n">
         <v>0</v>
       </c>
-      <c r="Q177" t="n">
-        <v>0</v>
-      </c>
       <c r="R177" t="n">
         <v>0</v>
       </c>
@@ -32509,9 +32302,6 @@
       <c r="O180" t="n">
         <v>0</v>
       </c>
-      <c r="Q180" t="n">
-        <v>0</v>
-      </c>
       <c r="R180" t="n">
         <v>0</v>
       </c>
@@ -33053,9 +32843,6 @@
       <c r="O183" t="n">
         <v>21</v>
       </c>
-      <c r="Q183" t="n">
-        <v>0</v>
-      </c>
       <c r="R183" t="n">
         <v>0.0443982885474583</v>
       </c>
@@ -33201,9 +32988,6 @@
       <c r="O184" t="n">
         <v>0</v>
       </c>
-      <c r="Q184" t="n">
-        <v>0</v>
-      </c>
       <c r="R184" t="n">
         <v>0</v>
       </c>
@@ -33745,9 +33529,6 @@
       <c r="O187" t="n">
         <v>0</v>
       </c>
-      <c r="Q187" t="n">
-        <v>0</v>
-      </c>
       <c r="R187" t="n">
         <v>0</v>
       </c>
@@ -34289,9 +34070,6 @@
       <c r="O190" t="n">
         <v>24</v>
       </c>
-      <c r="Q190" t="n">
-        <v>0</v>
-      </c>
       <c r="R190" t="n">
         <v>0.05074090119709519</v>
       </c>
@@ -34437,9 +34215,6 @@
       <c r="O191" t="n">
         <v>2</v>
       </c>
-      <c r="Q191" t="n">
-        <v>0</v>
-      </c>
       <c r="R191" t="n">
         <v>0.04407214257161833</v>
       </c>
@@ -34981,9 +34756,6 @@
       <c r="O194" t="n">
         <v>1</v>
       </c>
-      <c r="Q194" t="n">
-        <v>0</v>
-      </c>
       <c r="R194" t="n">
         <v>0.01922875021199697</v>
       </c>
@@ -35525,9 +35297,6 @@
       <c r="O197" t="n">
         <v>19</v>
       </c>
-      <c r="Q197" t="n">
-        <v>0</v>
-      </c>
       <c r="R197" t="n">
         <v>0.04016988011436703</v>
       </c>
@@ -35673,9 +35442,6 @@
       <c r="O198" t="n">
         <v>0</v>
       </c>
-      <c r="Q198" t="n">
-        <v>0</v>
-      </c>
       <c r="R198" t="n">
         <v>0</v>
       </c>
@@ -36217,9 +35983,6 @@
       <c r="O201" t="n">
         <v>0</v>
       </c>
-      <c r="Q201" t="n">
-        <v>0</v>
-      </c>
       <c r="R201" t="n">
         <v>0</v>
       </c>
@@ -36761,9 +36524,6 @@
       <c r="O204" t="n">
         <v>19</v>
       </c>
-      <c r="Q204" t="n">
-        <v>0</v>
-      </c>
       <c r="R204" t="n">
         <v>0.04016988011436703</v>
       </c>
@@ -36909,9 +36669,6 @@
       <c r="O205" t="n">
         <v>1</v>
       </c>
-      <c r="Q205" t="n">
-        <v>0</v>
-      </c>
       <c r="R205" t="n">
         <v>0.02203607128580917</v>
       </c>
@@ -37453,9 +37210,6 @@
       <c r="O208" t="n">
         <v>0</v>
       </c>
-      <c r="Q208" t="n">
-        <v>0</v>
-      </c>
       <c r="R208" t="n">
         <v>0</v>
       </c>
@@ -37997,9 +37751,6 @@
       <c r="O211" t="n">
         <v>18</v>
       </c>
-      <c r="Q211" t="n">
-        <v>0</v>
-      </c>
       <c r="R211" t="n">
         <v>0.0380556758978214</v>
       </c>
@@ -38145,9 +37896,6 @@
       <c r="O212" t="n">
         <v>0</v>
       </c>
-      <c r="Q212" t="n">
-        <v>0</v>
-      </c>
       <c r="R212" t="n">
         <v>0</v>
       </c>
@@ -38689,9 +38437,6 @@
       <c r="O215" t="n">
         <v>0</v>
       </c>
-      <c r="Q215" t="n">
-        <v>0</v>
-      </c>
       <c r="R215" t="n">
         <v>0</v>
       </c>
@@ -39233,9 +38978,6 @@
       <c r="O218" t="n">
         <v>10</v>
       </c>
-      <c r="Q218" t="n">
-        <v>0</v>
-      </c>
       <c r="R218" t="n">
         <v>0.02114204216545633</v>
       </c>
@@ -39381,9 +39123,6 @@
       <c r="O219" t="n">
         <v>5</v>
       </c>
-      <c r="Q219" t="n">
-        <v>0</v>
-      </c>
       <c r="R219" t="n">
         <v>0.1101803564290458</v>
       </c>
@@ -39925,9 +39664,6 @@
       <c r="O222" t="n">
         <v>1</v>
       </c>
-      <c r="Q222" t="n">
-        <v>0</v>
-      </c>
       <c r="R222" t="n">
         <v>0.01922875021199697</v>
       </c>
@@ -40469,9 +40205,6 @@
       <c r="O225" t="n">
         <v>9</v>
       </c>
-      <c r="Q225" t="n">
-        <v>0</v>
-      </c>
       <c r="R225" t="n">
         <v>0.0190278379489107</v>
       </c>
@@ -40617,9 +40350,6 @@
       <c r="O226" t="n">
         <v>2</v>
       </c>
-      <c r="Q226" t="n">
-        <v>0</v>
-      </c>
       <c r="R226" t="n">
         <v>0.04407214257161833</v>
       </c>
@@ -41161,9 +40891,6 @@
       <c r="O229" t="n">
         <v>0</v>
       </c>
-      <c r="Q229" t="n">
-        <v>0</v>
-      </c>
       <c r="R229" t="n">
         <v>0</v>
       </c>
@@ -41705,9 +41432,6 @@
       <c r="O232" t="n">
         <v>7</v>
       </c>
-      <c r="Q232" t="n">
-        <v>0</v>
-      </c>
       <c r="R232" t="n">
         <v>0.01479942951581943</v>
       </c>
@@ -41853,9 +41577,6 @@
       <c r="O233" t="n">
         <v>1</v>
       </c>
-      <c r="Q233" t="n">
-        <v>0</v>
-      </c>
       <c r="R233" t="n">
         <v>0.02203607128580917</v>
       </c>
@@ -42397,9 +42118,6 @@
       <c r="O236" t="n">
         <v>0</v>
       </c>
-      <c r="Q236" t="n">
-        <v>0</v>
-      </c>
       <c r="R236" t="n">
         <v>0</v>
       </c>
@@ -42941,9 +42659,6 @@
       <c r="O239" t="n">
         <v>12</v>
       </c>
-      <c r="Q239" t="n">
-        <v>0</v>
-      </c>
       <c r="R239" t="n">
         <v>0.0253704505985476</v>
       </c>
@@ -43089,9 +42804,6 @@
       <c r="O240" t="n">
         <v>2</v>
       </c>
-      <c r="Q240" t="n">
-        <v>0</v>
-      </c>
       <c r="R240" t="n">
         <v>0.04407214257161833</v>
       </c>
@@ -43633,9 +43345,6 @@
       <c r="O243" t="n">
         <v>0</v>
       </c>
-      <c r="Q243" t="n">
-        <v>0</v>
-      </c>
       <c r="R243" t="n">
         <v>0</v>
       </c>
@@ -44177,9 +43886,6 @@
       <c r="O246" t="n">
         <v>20</v>
       </c>
-      <c r="Q246" t="n">
-        <v>0</v>
-      </c>
       <c r="R246" t="n">
         <v>0.04209271465503427</v>
       </c>
@@ -44325,9 +44031,6 @@
       <c r="O247" t="n">
         <v>0</v>
       </c>
-      <c r="Q247" t="n">
-        <v>0</v>
-      </c>
       <c r="R247" t="n">
         <v>0</v>
       </c>
@@ -45017,9 +44720,6 @@
       <c r="O251" t="n">
         <v>0</v>
       </c>
-      <c r="Q251" t="n">
-        <v>0</v>
-      </c>
       <c r="R251" t="n">
         <v>0</v>
       </c>
@@ -45561,9 +45261,6 @@
       <c r="O254" t="n">
         <v>22</v>
       </c>
-      <c r="Q254" t="n">
-        <v>0</v>
-      </c>
       <c r="R254" t="n">
         <v>0.04630198612053769</v>
       </c>
@@ -45709,9 +45406,6 @@
       <c r="O255" t="n">
         <v>0</v>
       </c>
-      <c r="Q255" t="n">
-        <v>0</v>
-      </c>
       <c r="R255" t="n">
         <v>0</v>
       </c>
@@ -46401,9 +46095,6 @@
       <c r="O259" t="n">
         <v>1</v>
       </c>
-      <c r="Q259" t="n">
-        <v>0</v>
-      </c>
       <c r="R259" t="n">
         <v>0.01918297779282576</v>
       </c>
@@ -46945,9 +46636,6 @@
       <c r="O262" t="n">
         <v>21</v>
       </c>
-      <c r="Q262" t="n">
-        <v>0</v>
-      </c>
       <c r="R262" t="n">
         <v>0.04419735038778597</v>
       </c>
@@ -47093,9 +46781,6 @@
       <c r="O263" t="n">
         <v>1</v>
       </c>
-      <c r="Q263" t="n">
-        <v>0</v>
-      </c>
       <c r="R263" t="n">
         <v>0.02190739350432638</v>
       </c>
@@ -47785,9 +47470,6 @@
       <c r="O267" t="n">
         <v>1</v>
       </c>
-      <c r="Q267" t="n">
-        <v>0</v>
-      </c>
       <c r="R267" t="n">
         <v>0.01918297779282576</v>
       </c>
@@ -48329,9 +48011,6 @@
       <c r="O270" t="n">
         <v>29</v>
       </c>
-      <c r="Q270" t="n">
-        <v>0</v>
-      </c>
       <c r="R270" t="n">
         <v>0.06103443624979968</v>
       </c>
@@ -48477,9 +48156,6 @@
       <c r="O271" t="n">
         <v>1</v>
       </c>
-      <c r="Q271" t="n">
-        <v>0</v>
-      </c>
       <c r="R271" t="n">
         <v>0.02190739350432638</v>
       </c>
@@ -49169,9 +48845,6 @@
       <c r="O275" t="n">
         <v>1</v>
       </c>
-      <c r="Q275" t="n">
-        <v>0</v>
-      </c>
       <c r="R275" t="n">
         <v>0.01918297779282576</v>
       </c>
@@ -49713,9 +49386,6 @@
       <c r="O278" t="n">
         <v>20</v>
       </c>
-      <c r="Q278" t="n">
-        <v>0</v>
-      </c>
       <c r="R278" t="n">
         <v>0.04209271465503427</v>
       </c>
@@ -49861,9 +49531,6 @@
       <c r="O279" t="n">
         <v>1</v>
       </c>
-      <c r="Q279" t="n">
-        <v>0</v>
-      </c>
       <c r="R279" t="n">
         <v>0.02190739350432638</v>
       </c>
@@ -50553,9 +50220,6 @@
       <c r="O283" t="n">
         <v>0</v>
       </c>
-      <c r="Q283" t="n">
-        <v>0</v>
-      </c>
       <c r="R283" t="n">
         <v>0</v>
       </c>
@@ -51097,9 +50761,6 @@
       <c r="O286" t="n">
         <v>27</v>
       </c>
-      <c r="Q286" t="n">
-        <v>0</v>
-      </c>
       <c r="R286" t="n">
         <v>0.05682516478429625</v>
       </c>
@@ -51245,9 +50906,6 @@
       <c r="O287" t="n">
         <v>1</v>
       </c>
-      <c r="Q287" t="n">
-        <v>0</v>
-      </c>
       <c r="R287" t="n">
         <v>0.02190739350432638</v>
       </c>
@@ -51937,9 +51595,6 @@
       <c r="O291" t="n">
         <v>0</v>
       </c>
-      <c r="Q291" t="n">
-        <v>0</v>
-      </c>
       <c r="R291" t="n">
         <v>0</v>
       </c>
@@ -52481,9 +52136,6 @@
       <c r="O294" t="n">
         <v>11</v>
       </c>
-      <c r="Q294" t="n">
-        <v>0</v>
-      </c>
       <c r="R294" t="n">
         <v>0.02315099306026884</v>
       </c>
@@ -52629,9 +52281,6 @@
       <c r="O295" t="n">
         <v>1</v>
       </c>
-      <c r="Q295" t="n">
-        <v>0</v>
-      </c>
       <c r="R295" t="n">
         <v>0.02190739350432638</v>
       </c>
@@ -53173,9 +52822,6 @@
       <c r="O298" t="n">
         <v>1</v>
       </c>
-      <c r="Q298" t="n">
-        <v>0</v>
-      </c>
       <c r="R298" t="n">
         <v>0.01918297779282576</v>
       </c>
@@ -53717,9 +53363,6 @@
       <c r="O301" t="n">
         <v>17</v>
       </c>
-      <c r="Q301" t="n">
-        <v>0</v>
-      </c>
       <c r="R301" t="n">
         <v>0.03577880745677912</v>
       </c>
@@ -53865,9 +53508,6 @@
       <c r="O302" t="n">
         <v>1</v>
       </c>
-      <c r="Q302" t="n">
-        <v>0</v>
-      </c>
       <c r="R302" t="n">
         <v>0.02190739350432638</v>
       </c>
@@ -54557,9 +54197,6 @@
       <c r="O306" t="n">
         <v>0</v>
       </c>
-      <c r="Q306" t="n">
-        <v>0</v>
-      </c>
       <c r="R306" t="n">
         <v>0</v>
       </c>
@@ -55101,9 +54738,6 @@
       <c r="O309" t="n">
         <v>10</v>
       </c>
-      <c r="Q309" t="n">
-        <v>0</v>
-      </c>
       <c r="R309" t="n">
         <v>0.02104635732751713</v>
       </c>
@@ -55249,9 +54883,6 @@
       <c r="O310" t="n">
         <v>2</v>
       </c>
-      <c r="Q310" t="n">
-        <v>0</v>
-      </c>
       <c r="R310" t="n">
         <v>0.04381478700865277</v>
       </c>
@@ -55941,9 +55572,6 @@
       <c r="O314" t="n">
         <v>0</v>
       </c>
-      <c r="Q314" t="n">
-        <v>0</v>
-      </c>
       <c r="R314" t="n">
         <v>0</v>
       </c>
@@ -56485,9 +56113,6 @@
       <c r="O317" t="n">
         <v>11</v>
       </c>
-      <c r="Q317" t="n">
-        <v>0</v>
-      </c>
       <c r="R317" t="n">
         <v>0.02315099306026884</v>
       </c>
@@ -56633,9 +56258,6 @@
       <c r="O318" t="n">
         <v>2</v>
       </c>
-      <c r="Q318" t="n">
-        <v>0</v>
-      </c>
       <c r="R318" t="n">
         <v>0.04381478700865277</v>
       </c>
@@ -57325,9 +56947,6 @@
       <c r="O322" t="n">
         <v>1</v>
       </c>
-      <c r="Q322" t="n">
-        <v>0</v>
-      </c>
       <c r="R322" t="n">
         <v>0.01918297779282576</v>
       </c>
@@ -57869,9 +57488,6 @@
       <c r="O325" t="n">
         <v>6</v>
       </c>
-      <c r="Q325" t="n">
-        <v>0</v>
-      </c>
       <c r="R325" t="n">
         <v>0.01262781439651028</v>
       </c>
@@ -58017,9 +57633,6 @@
       <c r="O326" t="n">
         <v>0</v>
       </c>
-      <c r="Q326" t="n">
-        <v>0</v>
-      </c>
       <c r="R326" t="n">
         <v>0</v>
       </c>
@@ -58709,9 +58322,6 @@
       <c r="O330" t="n">
         <v>1</v>
       </c>
-      <c r="Q330" t="n">
-        <v>0</v>
-      </c>
       <c r="R330" t="n">
         <v>0.01918297779282576</v>
       </c>
@@ -59253,9 +58863,6 @@
       <c r="O333" t="n">
         <v>5</v>
       </c>
-      <c r="Q333" t="n">
-        <v>0</v>
-      </c>
       <c r="R333" t="n">
         <v>0.01052317866375857</v>
       </c>
@@ -59401,9 +59008,6 @@
       <c r="O334" t="n">
         <v>1</v>
       </c>
-      <c r="Q334" t="n">
-        <v>0</v>
-      </c>
       <c r="R334" t="n">
         <v>0.02190739350432638</v>
       </c>
@@ -60093,9 +59697,6 @@
       <c r="O338" t="n">
         <v>1</v>
       </c>
-      <c r="Q338" t="n">
-        <v>0</v>
-      </c>
       <c r="R338" t="n">
         <v>0.01912723205234435</v>
       </c>
@@ -60637,9 +60238,6 @@
       <c r="O341" t="n">
         <v>17</v>
       </c>
-      <c r="Q341" t="n">
-        <v>0</v>
-      </c>
       <c r="R341" t="n">
         <v>0.03564159819400248</v>
       </c>
@@ -60785,9 +60383,6 @@
       <c r="O342" t="n">
         <v>0</v>
       </c>
-      <c r="Q342" t="n">
-        <v>0</v>
-      </c>
       <c r="R342" t="n">
         <v>0</v>
       </c>
@@ -61477,9 +61072,6 @@
       <c r="O346" t="n">
         <v>1</v>
       </c>
-      <c r="Q346" t="n">
-        <v>0</v>
-      </c>
       <c r="R346" t="n">
         <v>0.01912723205234435</v>
       </c>
@@ -62021,9 +61613,6 @@
       <c r="O349" t="n">
         <v>15</v>
       </c>
-      <c r="Q349" t="n">
-        <v>0</v>
-      </c>
       <c r="R349" t="n">
         <v>0.03144846899470807</v>
       </c>
@@ -62169,9 +61758,6 @@
       <c r="O350" t="n">
         <v>0</v>
       </c>
-      <c r="Q350" t="n">
-        <v>0</v>
-      </c>
       <c r="R350" t="n">
         <v>0</v>
       </c>
@@ -62861,9 +62447,6 @@
       <c r="O354" t="n">
         <v>0</v>
       </c>
-      <c r="Q354" t="n">
-        <v>0</v>
-      </c>
       <c r="R354" t="n">
         <v>0</v>
       </c>
@@ -63405,9 +62988,6 @@
       <c r="O357" t="n">
         <v>17</v>
       </c>
-      <c r="Q357" t="n">
-        <v>0</v>
-      </c>
       <c r="R357" t="n">
         <v>0.03564159819400248</v>
       </c>
@@ -63553,9 +63133,6 @@
       <c r="O358" t="n">
         <v>0</v>
       </c>
-      <c r="Q358" t="n">
-        <v>0</v>
-      </c>
       <c r="R358" t="n">
         <v>0</v>
       </c>
@@ -64245,9 +63822,6 @@
       <c r="O362" t="n">
         <v>1</v>
       </c>
-      <c r="Q362" t="n">
-        <v>0</v>
-      </c>
       <c r="R362" t="n">
         <v>0.01912723205234435</v>
       </c>
@@ -64789,9 +64363,6 @@
       <c r="O365" t="n">
         <v>17</v>
       </c>
-      <c r="Q365" t="n">
-        <v>0</v>
-      </c>
       <c r="R365" t="n">
         <v>0.03564159819400248</v>
       </c>
@@ -64937,9 +64508,6 @@
       <c r="O366" t="n">
         <v>3</v>
       </c>
-      <c r="Q366" t="n">
-        <v>0</v>
-      </c>
       <c r="R366" t="n">
         <v>0.06533467414603497</v>
       </c>
@@ -65629,9 +65197,6 @@
       <c r="O370" t="n">
         <v>0</v>
       </c>
-      <c r="Q370" t="n">
-        <v>0</v>
-      </c>
       <c r="R370" t="n">
         <v>0</v>
       </c>
@@ -66173,9 +65738,6 @@
       <c r="O373" t="n">
         <v>21</v>
       </c>
-      <c r="Q373" t="n">
-        <v>0</v>
-      </c>
       <c r="R373" t="n">
         <v>0.0440278565925913</v>
       </c>
@@ -66321,9 +65883,6 @@
       <c r="O374" t="n">
         <v>0</v>
       </c>
-      <c r="Q374" t="n">
-        <v>0</v>
-      </c>
       <c r="R374" t="n">
         <v>0</v>
       </c>
@@ -67013,9 +66572,6 @@
       <c r="O378" t="n">
         <v>0</v>
       </c>
-      <c r="Q378" t="n">
-        <v>0</v>
-      </c>
       <c r="R378" t="n">
         <v>0</v>
       </c>
@@ -67557,9 +67113,6 @@
       <c r="O381" t="n">
         <v>15</v>
       </c>
-      <c r="Q381" t="n">
-        <v>0</v>
-      </c>
       <c r="R381" t="n">
         <v>0.03144846899470807</v>
       </c>
@@ -67705,9 +67258,6 @@
       <c r="O382" t="n">
         <v>3</v>
       </c>
-      <c r="Q382" t="n">
-        <v>0</v>
-      </c>
       <c r="R382" t="n">
         <v>0.06533467414603497</v>
       </c>
@@ -68397,9 +67947,6 @@
       <c r="O386" t="n">
         <v>1</v>
       </c>
-      <c r="Q386" t="n">
-        <v>0</v>
-      </c>
       <c r="R386" t="n">
         <v>0.01912723205234435</v>
       </c>
@@ -68941,9 +68488,6 @@
       <c r="O389" t="n">
         <v>20</v>
       </c>
-      <c r="Q389" t="n">
-        <v>0</v>
-      </c>
       <c r="R389" t="n">
         <v>0.0419312919929441</v>
       </c>
@@ -69089,9 +68633,6 @@
       <c r="O390" t="n">
         <v>1</v>
       </c>
-      <c r="Q390" t="n">
-        <v>0</v>
-      </c>
       <c r="R390" t="n">
         <v>0.02177822471534499</v>
       </c>
@@ -69781,9 +69322,6 @@
       <c r="O394" t="n">
         <v>1</v>
       </c>
-      <c r="Q394" t="n">
-        <v>0</v>
-      </c>
       <c r="R394" t="n">
         <v>0.01912723205234435</v>
       </c>
@@ -70325,9 +69863,6 @@
       <c r="O397" t="n">
         <v>8</v>
       </c>
-      <c r="Q397" t="n">
-        <v>0</v>
-      </c>
       <c r="R397" t="n">
         <v>0.01677251679717764</v>
       </c>
@@ -70473,9 +70008,6 @@
       <c r="O398" t="n">
         <v>4</v>
       </c>
-      <c r="Q398" t="n">
-        <v>0</v>
-      </c>
       <c r="R398" t="n">
         <v>0.08711289886137998</v>
       </c>
@@ -71165,9 +70697,6 @@
       <c r="O402" t="n">
         <v>0</v>
       </c>
-      <c r="Q402" t="n">
-        <v>0</v>
-      </c>
       <c r="R402" t="n">
         <v>0</v>
       </c>
@@ -71709,9 +71238,6 @@
       <c r="O405" t="n">
         <v>8</v>
       </c>
-      <c r="Q405" t="n">
-        <v>0</v>
-      </c>
       <c r="R405" t="n">
         <v>0.01677251679717764</v>
       </c>
@@ -71857,9 +71383,6 @@
       <c r="O406" t="n">
         <v>2</v>
       </c>
-      <c r="Q406" t="n">
-        <v>0</v>
-      </c>
       <c r="R406" t="n">
         <v>0.04355644943068999</v>
       </c>
@@ -72549,9 +72072,6 @@
       <c r="O410" t="n">
         <v>0</v>
       </c>
-      <c r="Q410" t="n">
-        <v>0</v>
-      </c>
       <c r="R410" t="n">
         <v>0</v>
       </c>
@@ -73093,9 +72613,6 @@
       <c r="O413" t="n">
         <v>10</v>
       </c>
-      <c r="Q413" t="n">
-        <v>0</v>
-      </c>
       <c r="R413" t="n">
         <v>0.02096564599647205</v>
       </c>
@@ -73241,9 +72758,6 @@
       <c r="O414" t="n">
         <v>1</v>
       </c>
-      <c r="Q414" t="n">
-        <v>0</v>
-      </c>
       <c r="R414" t="n">
         <v>0.02177822471534499</v>
       </c>
@@ -73933,9 +73447,6 @@
       <c r="O418" t="n">
         <v>0</v>
       </c>
-      <c r="Q418" t="n">
-        <v>0</v>
-      </c>
       <c r="R418" t="n">
         <v>0</v>
       </c>
@@ -74477,9 +73988,6 @@
       <c r="O421" t="n">
         <v>10</v>
       </c>
-      <c r="Q421" t="n">
-        <v>0</v>
-      </c>
       <c r="R421" t="n">
         <v>0.02096564599647205</v>
       </c>
@@ -74625,9 +74133,6 @@
       <c r="O422" t="n">
         <v>0</v>
       </c>
-      <c r="Q422" t="n">
-        <v>0</v>
-      </c>
       <c r="R422" t="n">
         <v>0</v>
       </c>
@@ -75317,9 +74822,6 @@
       <c r="O426" t="n">
         <v>0</v>
       </c>
-      <c r="Q426" t="n">
-        <v>0</v>
-      </c>
       <c r="R426" t="n">
         <v>0</v>
       </c>
@@ -75861,9 +75363,6 @@
       <c r="O429" t="n">
         <v>16</v>
       </c>
-      <c r="Q429" t="n">
-        <v>0</v>
-      </c>
       <c r="R429" t="n">
         <v>0.03354503359435528</v>
       </c>
@@ -76007,9 +75506,6 @@
         <v>0</v>
       </c>
       <c r="O430" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q430" t="n">
         <v>0</v>
       </c>
       <c r="R430" t="n">
